--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92553587096</v>
+        <v>46157.9310773767</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9310773767</v>
+        <v>46157.93132558106</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93132558106</v>
+        <v>46157.9338048895</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9338048895</v>
+        <v>46157.93691252789</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93691252789</v>
+        <v>46158.28203328626</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28203328626</v>
+        <v>46158.29734884817</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29734884817</v>
+        <v>46158.29803735505</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29803735505</v>
+        <v>46158.33367342164</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33367342164</v>
+        <v>46158.37219145583</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37219145583</v>
+        <v>46158.37273887562</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
